--- a/tables/new/imb all/all_ROC_AUC.xlsx
+++ b/tables/new/imb all/all_ROC_AUC.xlsx
@@ -682,52 +682,52 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7506392183227705</v>
+        <v>0.7484809591792043</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8100549653154248</v>
+        <v>0.8390170131895112</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7613004944270325</v>
+        <v>0.7683559852742645</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8078972211970571</v>
+        <v>0.8279449008447881</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7494040829510477</v>
+        <v>0.751079137894419</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8153643856371502</v>
+        <v>0.8252002570250609</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7640174953187668</v>
+        <v>0.743607067504837</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8205003113739783</v>
+        <v>0.8355889861851098</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7666577017838299</v>
+        <v>0.7550117649615689</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8058392846026152</v>
+        <v>0.8263612991910682</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7525631929292718</v>
+        <v>0.7698686809345732</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8137869646380721</v>
+        <v>0.8310538320783639</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7488435911990055</v>
+        <v>0.7706566182637145</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7942890296817697</v>
+        <v>0.8156348006878869</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7581399077861342</v>
+        <v>0.7739951221038244</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.7775391281082421</v>
+        <v>0.8113412843928379</v>
       </c>
     </row>
     <row r="6">
@@ -843,221 +843,221 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>synth_credit_card_fraud_label_ROC_AUC.csv</t>
+          <t>kdd_ROC_AUC.csv</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9779664880884532</v>
+        <v>0.5217933603207073</v>
       </c>
       <c r="C8" t="n">
-        <v>0.984734412401687</v>
+        <v>0.5269277159758483</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9800866294312094</v>
+        <v>0.5276241668507725</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9807705459933888</v>
+        <v>0.5171824630326862</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9759945286675024</v>
+        <v>0.5263510976506007</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9828678901174056</v>
+        <v>0.5356215274765859</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9762623959876896</v>
+        <v>0.5222087186336476</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9841160378433832</v>
+        <v>0.5411772963909067</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9729681978798588</v>
+        <v>0.5255292885415355</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9850678217257496</v>
+        <v>0.5328166719089811</v>
       </c>
       <c r="L8" t="n">
-        <v>0.9791576427675824</v>
+        <v>0.5287959398178579</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9832411945742618</v>
+        <v>0.5267688530069703</v>
       </c>
       <c r="N8" t="n">
-        <v>0.9803146016186026</v>
+        <v>0.5273760243269079</v>
       </c>
       <c r="O8" t="n">
-        <v>0.981907557278012</v>
+        <v>0.5260271843351658</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9808446369542916</v>
+        <v>0.5266947229100457</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.9809472244386184</v>
+        <v>0.5139647176642512</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>synth_mobile_money_fraud_label_ROC_AUC.csv</t>
+          <t>synth_credit_card_fraud_label_ROC_AUC.csv</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9517596616208888</v>
+        <v>0.9779664880884532</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9891622918971044</v>
+        <v>0.984734412401687</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9475030501561176</v>
+        <v>0.9800866294312094</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9929164681357951</v>
+        <v>0.9807705459933888</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9453801737274042</v>
+        <v>0.9759945286675024</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9917156000144388</v>
+        <v>0.9828678901174056</v>
       </c>
       <c r="H9" t="n">
-        <v>0.940992770382288</v>
+        <v>0.9762623959876896</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9913616168921412</v>
+        <v>0.9841160378433832</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9474820742092928</v>
+        <v>0.9729681978798588</v>
       </c>
       <c r="K9" t="n">
-        <v>0.988602481249146</v>
+        <v>0.9850678217257496</v>
       </c>
       <c r="L9" t="n">
-        <v>0.9581631440328582</v>
+        <v>0.9791576427675824</v>
       </c>
       <c r="M9" t="n">
-        <v>0.9920530225680612</v>
+        <v>0.9832411945742618</v>
       </c>
       <c r="N9" t="n">
-        <v>0.9490309263398899</v>
+        <v>0.9803146016186026</v>
       </c>
       <c r="O9" t="n">
-        <v>0.9910818669121232</v>
+        <v>0.981907557278012</v>
       </c>
       <c r="P9" t="n">
-        <v>0.946214926427553</v>
+        <v>0.9808446369542916</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.9884774905955668</v>
+        <v>0.9809472244386184</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>telco_customer_churn_ROC_AUC.csv</t>
+          <t>synth_mobile_money_fraud_label_ROC_AUC.csv</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7712015433266675</v>
+        <v>0.9517596616208888</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8197175377804857</v>
+        <v>0.9891622918971044</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8166840787119661</v>
+        <v>0.9475030501561176</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5910643071460518</v>
+        <v>0.9929164681357951</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7680401578563902</v>
+        <v>0.9453801737274042</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8197977980876632</v>
+        <v>0.9917156000144388</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7955366454895971</v>
+        <v>0.940992770382288</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8141940582243963</v>
+        <v>0.9913616168921412</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7795745981610667</v>
+        <v>0.9474820742092928</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8254444810261332</v>
+        <v>0.988602481249146</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8164138656405653</v>
+        <v>0.9581631440328582</v>
       </c>
       <c r="M10" t="n">
-        <v>0.677596150792525</v>
+        <v>0.9920530225680612</v>
       </c>
       <c r="N10" t="n">
-        <v>0.8160856754539733</v>
+        <v>0.9490309263398899</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6693573439727976</v>
+        <v>0.9910818669121232</v>
       </c>
       <c r="P10" t="n">
-        <v>0.8162927427474767</v>
+        <v>0.946214926427553</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.6689939905739033</v>
+        <v>0.9884774905955668</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>ulb_credit_card_fraud_label_ROC_AUC.csv</t>
+          <t>telco_customer_churn_ROC_AUC.csv</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9763423555732462</v>
+        <v>0.7712015433266675</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9755620027359532</v>
+        <v>0.8197175377804857</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9810699383724282</v>
+        <v>0.8166840787119661</v>
       </c>
       <c r="E11" t="n">
-        <v>0.977437823407497</v>
+        <v>0.5910643071460518</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9771127002209808</v>
+        <v>0.7680401578563902</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9822537642230672</v>
+        <v>0.8197977980876632</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9742949659378416</v>
+        <v>0.7955366454895971</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9769108207401712</v>
+        <v>0.8141940582243963</v>
       </c>
       <c r="J11" t="n">
-        <v>0.974643250934479</v>
+        <v>0.7795745981610667</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9777978322833312</v>
+        <v>0.8254444810261332</v>
       </c>
       <c r="L11" t="n">
-        <v>0.9783605784847944</v>
+        <v>0.8164138656405653</v>
       </c>
       <c r="M11" t="n">
-        <v>0.977037209876882</v>
+        <v>0.677596150792525</v>
       </c>
       <c r="N11" t="n">
-        <v>0.9788180957217564</v>
+        <v>0.8160856754539733</v>
       </c>
       <c r="O11" t="n">
-        <v>0.9816601356081091</v>
+        <v>0.6693573439727976</v>
       </c>
       <c r="P11" t="n">
-        <v>0.974538593866524</v>
+        <v>0.8162927427474767</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.9795495514043492</v>
+        <v>0.6689939905739033</v>
       </c>
     </row>
     <row r="12">

--- a/tables/new/imb all/all_ROC_AUC.xlsx
+++ b/tables/new/imb all/all_ROC_AUC.xlsx
@@ -425,86 +425,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Logit(1, 1, 1, 1)_ABROOD</t>
+          <t>XGBoost(1, 1, 1, 1)_ABROOD</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>XGBoost(1, 1, 1, 1)_ABROOD</t>
+          <t>Logit(1, 1, 0, 0)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Logit(1, 1, 0, 0)</t>
+          <t>XGBoost(1, 1, 0, 0)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>XGBoost(1, 1, 0, 0)</t>
+          <t>XGBoost(1, 1, 1, 1)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Logit(1, 1, 1, 1)</t>
+          <t>XGBoost(1, 1, 1, 1)_ABROOD_rose</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>XGBoost(1, 1, 1, 1)</t>
+          <t>XGBoost(1, 1, 1, 1)_rose_BROOD</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Logit(1, 1, 1, 1)_ABROOD_rose</t>
+          <t>XGBoost(1, 1, 0, 0)_rose</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>XGBoost(1, 1, 1, 1)_ABROOD_rose</t>
+          <t>XGBoost(1, 1, 0, 0)_smote</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Logit(1, 1, 1, 1)_rose_BROOD</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>XGBoost(1, 1, 1, 1)_rose_BROOD</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Logit(1, 1, 0, 0)_rose</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>XGBoost(1, 1, 0, 0)_rose</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Logit(1, 1, 0, 0)_smote</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>XGBoost(1, 1, 0, 0)_smote</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Logit(1, 1, 0, 0)_adasyn</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>XGBoost(1, 1, 0, 0)_adasyn</t>
         </is>
@@ -513,606 +478,375 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>apata_credit_card_fraud_label_ROC_AUC.csv</t>
+          <t>bank_marketing_ROC_AUC.csv</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5024654539812348</v>
+        <v>0.9233370761332924</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7075415586628212</v>
+        <v>0.8970182240593791</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8101113656553856</v>
+        <v>0.9166237430011076</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5</v>
+        <v>0.9119669742802832</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7837629908850841</v>
+        <v>0.9177166801005168</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8526629793241088</v>
+        <v>0.9113686471179004</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7477756531950885</v>
+        <v>0.9320105301270252</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8081258442554123</v>
+        <v>0.9225962388093154</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7478654028695557</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.6554156322636389</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.8081421969503366</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.8093888047168778</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
+        <v>0.9082530894263388</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bank_marketing_ROC_AUC.csv</t>
+          <t>telco_customer_churn_ROC_AUC.csv</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9094001749992456</v>
+        <v>0.8197175377804857</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9233370761332924</v>
+        <v>0.8166840787119661</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8970182240593791</v>
+        <v>0.5910643071460518</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9166237430011076</v>
+        <v>0.8197977980876632</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9248790953487268</v>
+        <v>0.8141940582243963</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9119669742802832</v>
+        <v>0.8254444810261332</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9125946655402348</v>
+        <v>0.677596150792525</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9177166801005168</v>
+        <v>0.6693573439727976</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9203079943620932</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.9113686471179004</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.9130488661686804</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.9320105301270252</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.9095289459959224</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.9225962388093154</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.903347399364658</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.9082530894263388</v>
+        <v>0.6689939905739033</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>car_insurance_fraud_label_ROC_AUC.csv</t>
+          <t>kag_credit_card_approval_ROC_AUC.csv</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7300270372958169</v>
+        <v>0.5807481430034914</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6897720208152088</v>
+        <v>0.6182058324863144</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6765570530022935</v>
+        <v>0.5966988843337111</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7082189707628944</v>
+        <v>0.5985847315776979</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7125506428878448</v>
+        <v>0.6515191630325874</v>
       </c>
       <c r="G4" t="n">
-        <v>0.698707131239391</v>
+        <v>0.6178148296717093</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7455423823898911</v>
+        <v>0.6063868970687123</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7513324061038313</v>
+        <v>0.6020281993246253</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7481315850498524</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.7609980114853431</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.7280825459969953</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.7196394589119868</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.7331197735180501</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.723408341577488</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.7324490153663006</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.7175700617889804</v>
+        <v>0.5929212267134897</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>customer_trans_fraud_detection_label_ROC_AUC.csv</t>
+          <t>vub_credit_scoring_ROC_AUC.csv</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7484809591792043</v>
+        <v>0.7759540855552955</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8390170131895112</v>
+        <v>0.7747598843072253</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7683559852742645</v>
+        <v>0.7835060778858433</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8279449008447881</v>
+        <v>0.7773497244014729</v>
       </c>
       <c r="F5" t="n">
-        <v>0.751079137894419</v>
+        <v>0.7640920618417046</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8252002570250609</v>
+        <v>0.7642706044513065</v>
       </c>
       <c r="H5" t="n">
-        <v>0.743607067504837</v>
+        <v>0.7718005462811931</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8355889861851098</v>
+        <v>0.7527393010261534</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7550117649615689</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.8263612991910682</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.7698686809345732</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.8310538320783639</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.7706566182637145</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.8156348006878869</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.7739951221038244</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.8113412843928379</v>
+        <v>0.7746541535400462</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>financial_statement_fraud_label_ROC_AUC.csv</t>
+          <t>kdd_ROC_AUC.csv</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6897030863135941</v>
+        <v>0.5269277159758483</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7302492650009417</v>
+        <v>0.5276241668507725</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7081215962787346</v>
+        <v>0.5171824630326862</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7284696220862781</v>
+        <v>0.5356215274765859</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7056032042410196</v>
+        <v>0.5411772963909067</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7194247966980321</v>
+        <v>0.5328166719089811</v>
       </c>
       <c r="H6" t="n">
-        <v>0.702113514701346</v>
+        <v>0.5267688530069703</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7368192557469146</v>
+        <v>0.5260271843351658</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7118301135324451</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.7291698741834481</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.7124439025788436</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.7268511330041193</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.7139486169460619</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.7318016826496546</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0.7152962994810647</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.7170699061221258</v>
+        <v>0.5139647176642512</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>kag_credit_card_approval_ROC_AUC.csv</t>
+          <t>car_insurance_fraud_label_ROC_AUC.csv</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6174300702967318</v>
+        <v>0.6897720208152088</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5807481430034914</v>
+        <v>0.6765570530022935</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6182058324863144</v>
+        <v>0.7082189707628944</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5966988843337111</v>
+        <v>0.698707131239391</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6237218477804963</v>
+        <v>0.7513324061038313</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5985847315776979</v>
+        <v>0.7609980114853431</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5907071485154197</v>
+        <v>0.7196394589119868</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6515191630325874</v>
+        <v>0.723408341577488</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6110652721787581</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.6178148296717093</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.6175225332530387</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.6063868970687123</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.626074752421512</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.6020281993246253</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0.6270778158093038</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.5929212267134897</v>
+        <v>0.7175700617889804</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>kdd_ROC_AUC.csv</t>
+          <t>apata_credit_card_fraud_label_ROC_AUC.csv</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5217933603207073</v>
+        <v>0.7075415586628212</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5269277159758483</v>
+        <v>0.8101113656553856</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5276241668507725</v>
+        <v>0.5</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5171824630326862</v>
+        <v>0.8526629793241088</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5263510976506007</v>
+        <v>0.8081258442554123</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5356215274765859</v>
+        <v>0.6554156322636389</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5222087186336476</v>
+        <v>0.5</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5411772963909067</v>
+        <v>0.5</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5255292885415355</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.5328166719089811</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.5287959398178579</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.5267688530069703</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.5273760243269079</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.5260271843351658</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0.5266947229100457</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.5139647176642512</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>synth_credit_card_fraud_label_ROC_AUC.csv</t>
+          <t>financial_statement_fraud_label_ROC_AUC.csv</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9779664880884532</v>
+        <v>0.7302492650009417</v>
       </c>
       <c r="C9" t="n">
-        <v>0.984734412401687</v>
+        <v>0.7081215962787346</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9800866294312094</v>
+        <v>0.7284696220862781</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9807705459933888</v>
+        <v>0.7194247966980321</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9759945286675024</v>
+        <v>0.7368192557469146</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9828678901174056</v>
+        <v>0.7291698741834481</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9762623959876896</v>
+        <v>0.7268511330041193</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9841160378433832</v>
+        <v>0.7318016826496546</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9729681978798588</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.9850678217257496</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.9791576427675824</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.9832411945742618</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.9803146016186026</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.981907557278012</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0.9808446369542916</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.9809472244386184</v>
+        <v>0.7170699061221258</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>synth_mobile_money_fraud_label_ROC_AUC.csv</t>
+          <t>customer_trans_fraud_detection_label_ROC_AUC.csv</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9517596616208888</v>
+        <v>0.8390170131895112</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9891622918971044</v>
+        <v>0.7683559852742645</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9475030501561176</v>
+        <v>0.8279449008447881</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9929164681357951</v>
+        <v>0.8252002570250609</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9453801737274042</v>
+        <v>0.8355889861851098</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9917156000144388</v>
+        <v>0.8263612991910682</v>
       </c>
       <c r="H10" t="n">
-        <v>0.940992770382288</v>
+        <v>0.8310538320783639</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9913616168921412</v>
+        <v>0.8156348006878869</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9474820742092928</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.988602481249146</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.9581631440328582</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.9920530225680612</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.9490309263398899</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0.9910818669121232</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0.946214926427553</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0.9884774905955668</v>
+        <v>0.8113412843928379</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>telco_customer_churn_ROC_AUC.csv</t>
+          <t>synth_mobile_money_fraud_label_ROC_AUC.csv</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7712015433266675</v>
+        <v>0.9891622918971044</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8197175377804857</v>
+        <v>0.9475030501561176</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8166840787119661</v>
+        <v>0.9929164681357951</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5910643071460518</v>
+        <v>0.9917156000144388</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7680401578563902</v>
+        <v>0.9913616168921412</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8197977980876632</v>
+        <v>0.988602481249146</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7955366454895971</v>
+        <v>0.9920530225680612</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8141940582243963</v>
+        <v>0.9910818669121232</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7795745981610667</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.8254444810261332</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.8164138656405653</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0.677596150792525</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.8160856754539733</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.6693573439727976</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0.8162927427474767</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0.6689939905739033</v>
+        <v>0.9884774905955668</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>vub_credit_scoring_ROC_AUC.csv</t>
+          <t>synth_credit_card_fraud_label_ROC_AUC.csv</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7556523760779388</v>
+        <v>0.984734412401687</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7759540855552955</v>
+        <v>0.9800866294312094</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7747598843072253</v>
+        <v>0.9807705459933888</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7835060778858433</v>
+        <v>0.9828678901174056</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7564126362690523</v>
+        <v>0.9841160378433832</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7773497244014729</v>
+        <v>0.9850678217257496</v>
       </c>
       <c r="H12" t="n">
-        <v>0.743052956600246</v>
+        <v>0.9832411945742618</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7640920618417046</v>
+        <v>0.981907557278012</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7586904166210128</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.7642706044513065</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.7694605382059634</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.7718005462811931</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.770915121011002</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.7527393010261534</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0.7739545896865494</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0.7746541535400462</v>
+        <v>0.9809472244386184</v>
       </c>
     </row>
   </sheetData>
